--- a/code/data/combined/pelg+jmul-lcdm-free.xlsx
+++ b/code/data/combined/pelg+jmul-lcdm-free.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -472,25 +472,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>543831.9299773615</v>
+        <v>543831.9299773368</v>
       </c>
       <c r="C2" t="n">
-        <v>-985857.6471267341</v>
+        <v>-985857.6471268286</v>
       </c>
       <c r="D2" t="n">
-        <v>74888.07319691582</v>
+        <v>74888.0731969887</v>
       </c>
       <c r="E2" t="n">
-        <v>221829.0705369968</v>
+        <v>221829.0705370009</v>
       </c>
       <c r="F2" t="n">
-        <v>-10062.16793664806</v>
+        <v>-10062.16793666872</v>
       </c>
       <c r="G2" t="n">
-        <v>-22067.40475038245</v>
+        <v>-22067.40475038278</v>
       </c>
       <c r="H2" t="n">
-        <v>-8468.205857388548</v>
+        <v>-8468.205857389563</v>
       </c>
     </row>
     <row r="3">
@@ -500,25 +500,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-985857.6471268946</v>
+        <v>-985857.6471269734</v>
       </c>
       <c r="C3" t="n">
-        <v>2505464.025068455</v>
+        <v>2505464.025068569</v>
       </c>
       <c r="D3" t="n">
-        <v>-410464.011838738</v>
+        <v>-410464.0118386509</v>
       </c>
       <c r="E3" t="n">
-        <v>-423082.6601525479</v>
+        <v>-423082.6601525652</v>
       </c>
       <c r="F3" t="n">
-        <v>44839.01953056225</v>
+        <v>44839.0195304857</v>
       </c>
       <c r="G3" t="n">
-        <v>42500.38954619981</v>
+        <v>42500.38954619992</v>
       </c>
       <c r="H3" t="n">
-        <v>21380.71146028258</v>
+        <v>21380.71146028347</v>
       </c>
     </row>
     <row r="4">
@@ -528,25 +528,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>74888.07319717022</v>
+        <v>74888.07319730721</v>
       </c>
       <c r="C4" t="n">
-        <v>-410464.0118393301</v>
+        <v>-410464.0118392144</v>
       </c>
       <c r="D4" t="n">
-        <v>285152.2969910655</v>
+        <v>285152.296990771</v>
       </c>
       <c r="E4" t="n">
-        <v>48556.94444987269</v>
+        <v>48556.9444498735</v>
       </c>
       <c r="F4" t="n">
-        <v>-98803.12100756451</v>
+        <v>-98803.12100740388</v>
       </c>
       <c r="G4" t="n">
-        <v>-5392.025980891094</v>
+        <v>-5392.025980888749</v>
       </c>
       <c r="H4" t="n">
-        <v>-4066.114502414553</v>
+        <v>-4066.114502412972</v>
       </c>
     </row>
     <row r="5">
@@ -556,25 +556,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>221829.0705370707</v>
+        <v>221829.0705370922</v>
       </c>
       <c r="C5" t="n">
-        <v>-423082.6601526654</v>
+        <v>-423082.660152678</v>
       </c>
       <c r="D5" t="n">
-        <v>48556.9444497841</v>
+        <v>48556.94444974617</v>
       </c>
       <c r="E5" t="n">
-        <v>103838.2184716415</v>
+        <v>103838.2184716434</v>
       </c>
       <c r="F5" t="n">
-        <v>-17728.69561111001</v>
+        <v>-17728.69561108058</v>
       </c>
       <c r="G5" t="n">
-        <v>-10113.71201078542</v>
+        <v>-10113.71201078495</v>
       </c>
       <c r="H5" t="n">
-        <v>-3841.449517843331</v>
+        <v>-3841.449517843394</v>
       </c>
     </row>
     <row r="6">
@@ -584,25 +584,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-10062.16793667949</v>
+        <v>-10062.16793667324</v>
       </c>
       <c r="C6" t="n">
-        <v>44839.01953062016</v>
+        <v>44839.01953054254</v>
       </c>
       <c r="D6" t="n">
-        <v>-98803.12100751026</v>
+        <v>-98803.12100745973</v>
       </c>
       <c r="E6" t="n">
-        <v>-17728.69561110494</v>
+        <v>-17728.69561109248</v>
       </c>
       <c r="F6" t="n">
-        <v>82575.26717294577</v>
+        <v>82575.26717291948</v>
       </c>
       <c r="G6" t="n">
-        <v>3933.386347639293</v>
+        <v>3933.386347637553</v>
       </c>
       <c r="H6" t="n">
-        <v>457.330952358244</v>
+        <v>457.330952357445</v>
       </c>
     </row>
     <row r="7">
@@ -612,25 +612,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-22067.40475038106</v>
+        <v>-22067.40475038858</v>
       </c>
       <c r="C7" t="n">
-        <v>42500.38954618968</v>
+        <v>42500.38954621015</v>
       </c>
       <c r="D7" t="n">
-        <v>-5392.025980876083</v>
+        <v>-5392.025980875665</v>
       </c>
       <c r="E7" t="n">
-        <v>-10113.71201078002</v>
+        <v>-10113.71201078205</v>
       </c>
       <c r="F7" t="n">
-        <v>3933.386347636484</v>
+        <v>3933.386347630956</v>
       </c>
       <c r="G7" t="n">
-        <v>1160.792167775039</v>
+        <v>1160.792167775074</v>
       </c>
       <c r="H7" t="n">
-        <v>371.7432495556678</v>
+        <v>371.7432495558592</v>
       </c>
     </row>
     <row r="8">
@@ -640,25 +640,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-8468.205857392621</v>
+        <v>-8468.205857400657</v>
       </c>
       <c r="C8" t="n">
-        <v>21380.71146029089</v>
+        <v>21380.71146030205</v>
       </c>
       <c r="D8" t="n">
-        <v>-4066.114502411814</v>
+        <v>-4066.114502406067</v>
       </c>
       <c r="E8" t="n">
-        <v>-3841.44951784366</v>
+        <v>-3841.44951784536</v>
       </c>
       <c r="F8" t="n">
-        <v>457.3309523584617</v>
+        <v>457.3309523525655</v>
       </c>
       <c r="G8" t="n">
-        <v>371.7432495558994</v>
+        <v>371.7432495559427</v>
       </c>
       <c r="H8" t="n">
-        <v>198.3591353862848</v>
+        <v>198.3591353863791</v>
       </c>
     </row>
   </sheetData>
